--- a/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T14:02:34+00:00</t>
+    <t>2026-01-30T09:35:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T09:35:57+00:00</t>
+    <t>2026-01-30T10:15:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.1</t>
+    <t>3.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:15:26+00:00</t>
+    <t>2026-02-02T08:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T08:09:27+00:00</t>
+    <t>2026-02-02T08:10:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T08:10:43+00:00</t>
+    <t>2026-02-02T09:29:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0-ballot</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:29:40+00:00</t>
+    <t>2026-02-18T12:52:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T12:52:41+00:00</t>
+    <t>2026-02-23T17:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:17:29+00:00</t>
+    <t>2026-03-18T17:41:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil de la ressource Observation pour définir l’hémoglobine glyquée (Hb1Ac) mesurée en %.</t>
+    <t>Profil biologie de la ressource Observation pour définir l’hémoglobine glyquée (Hb1Ac) mesurée en %.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T17:41:07+00:00</t>
+    <t>2026-03-31T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:00:47+00:00</t>
+    <t>2026-05-06T11:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T11:42:59+00:00</t>
+    <t>2026-05-07T07:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T07:18:48+00:00</t>
+    <t>2026-05-07T07:24:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T07:24:38+00:00</t>
+    <t>2026-06-09T08:46:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -646,6 +646,10 @@
     <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Observation.extension:MesReasonForMeasurement</t>
   </si>
   <si>
@@ -660,10 +664,6 @@
   </si>
   <si>
     <t>Extension du Motif de la mesure, exprimé en texte libre.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -4526,7 +4526,7 @@
         <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>122</v>
@@ -4552,13 +4552,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>82</v>
@@ -4580,13 +4580,13 @@
         <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4646,7 +4646,7 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>122</v>

--- a/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
+++ b/main/ig/StructureDefinition-mesures-observation-hb1ac.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T08:46:34+00:00</t>
+    <t>2026-06-26T10:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
